--- a/model_templates/ark.CyTOFAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.CyTOFAssayMetadataTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15057,7 +15057,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="118">
   <si>
     <t>Component</t>
   </si>
@@ -15395,6 +15395,9 @@
     <t>Sony MA900</t>
   </si>
   <si>
+    <t>Spatial Genomics Gene Positioning System</t>
+  </si>
+  <si>
     <t>Thermo Fisher Attune CytPix</t>
   </si>
   <si>
@@ -15509,6 +15512,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -43200,6 +43207,11 @@
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" s="7" t="s">
         <v>107</v>
       </c>
     </row>

--- a/model_templates/ark.CyTOFAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.CyTOFAssayMetadataTemplate.xlsx
@@ -15057,7 +15057,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>Component</t>
   </si>
@@ -15393,9 +15393,6 @@
   </si>
   <si>
     <t>Sony MA900</t>
-  </si>
-  <si>
-    <t>Spatial Genomics Gene Positioning System</t>
   </si>
   <si>
     <t>Thermo Fisher Attune CytPix</t>
@@ -43207,11 +43204,6 @@
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="F45" s="7" t="s">
         <v>107</v>
       </c>
     </row>
